--- a/artfynd/A 47082-2021 artfynd.xlsx
+++ b/artfynd/A 47082-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47082-2021 artfynd.xlsx
+++ b/artfynd/A 47082-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -937,6 +937,152 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125298673</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Motås, Motås, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>347090</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6537553</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Observerades i äldre granskog med inslag av asp, lönn etc.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47082-2021 artfynd.xlsx
+++ b/artfynd/A 47082-2021 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>125298673</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>58001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 47082-2021 artfynd.xlsx
+++ b/artfynd/A 47082-2021 artfynd.xlsx
@@ -942,12 +942,7 @@
         <v>125298673</v>
       </c>
       <c r="B4" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47082-2021 artfynd.xlsx
+++ b/artfynd/A 47082-2021 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>125298673</v>
       </c>
       <c r="B4" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
